--- a/Documentation/Testing/Testing.xlsx
+++ b/Documentation/Testing/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diarmuid\Desktop\SETU_Code_Lab\Documentation\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644EEB86-E8A5-4145-AE1F-6B73E27668C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403C955F-0E32-42FD-8841-8798AAED3543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{AEF770C7-57FF-4E6E-9271-55DC3BE5003D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="197">
   <si>
     <t>TEST ID</t>
   </si>
@@ -2250,8 +2250,12 @@
       <c r="F18" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="2:9" ht="90" x14ac:dyDescent="0.25">
@@ -2270,8 +2274,12 @@
       <c r="F19" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">

--- a/Documentation/Testing/Testing.xlsx
+++ b/Documentation/Testing/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diarmuid\Desktop\SETU_Code_Lab\Documentation\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403C955F-0E32-42FD-8841-8798AAED3543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B56E450-C87C-421F-A90B-0C3B31AF4EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{AEF770C7-57FF-4E6E-9271-55DC3BE5003D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
   <si>
     <t>TEST ID</t>
   </si>
@@ -570,14 +570,6 @@
     <t>The system shall have 99% uptime</t>
   </si>
   <si>
-    <t>1. Set up an uptime check on Digital Ocean
-2. Wait 10 days
-3. Observe uptime</t>
-  </si>
-  <si>
-    <t>Uptime ≥ 99% over 10 days</t>
-  </si>
-  <si>
     <t>Results displayed within 30 seconds of submission</t>
   </si>
   <si>
@@ -694,15 +686,6 @@
     <t>No layout defects observed at this resolution</t>
   </si>
   <si>
-    <t>TC-NF06a</t>
-  </si>
-  <si>
-    <t>TC-NF06b</t>
-  </si>
-  <si>
-    <t>The system shall ensure submissions cannot access the server file system.</t>
-  </si>
-  <si>
     <t>The system shall ensure submissions cannot access the network.</t>
   </si>
   <si>
@@ -711,14 +694,6 @@
 4. Observe results</t>
   </si>
   <si>
-    <t>1. Log in as student
-2. Submit code that attempts to read a local file
-3. Observe results</t>
-  </si>
-  <si>
-    <t>No file contents are returned to the user</t>
-  </si>
-  <si>
     <t>No network response data is returned to the user</t>
   </si>
   <si>
@@ -748,10 +723,23 @@
     <t>Test case entry on createProblem screen way too small. Retested and now passing.</t>
   </si>
   <si>
-    <t>This was meant to be tested over a 30 day period however project timeline did not allow.</t>
-  </si>
-  <si>
     <t>Evidence</t>
+  </si>
+  <si>
+    <t>TC-NF06</t>
+  </si>
+  <si>
+    <t>Full flow completed in 62 seconds</t>
+  </si>
+  <si>
+    <t>1. Set up an uptime check on Digital Ocean
+2. Observe uptime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uptime ≥ 99% </t>
+  </si>
+  <si>
+    <t>Uptime is 99.69%</t>
   </si>
 </sst>
 </file>
@@ -1840,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65772ACC-7E16-4BF0-962A-A0C3B65DB5DB}">
-  <dimension ref="B2:I34"/>
+  <dimension ref="B2:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.42578125" customWidth="1"/>
@@ -1919,9 +1907,11 @@
         <v>129</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="2:9" ht="135" x14ac:dyDescent="0.25">
@@ -1946,7 +1936,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>139</v>
       </c>
@@ -1957,35 +1947,37 @@
         <v>144</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>12</v>
@@ -1994,116 +1986,120 @@
     </row>
     <row r="8" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="2:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>12</v>
@@ -2112,22 +2108,22 @@
     </row>
     <row r="13" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>12</v>
@@ -2136,98 +2132,98 @@
     </row>
     <row r="14" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="150" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>12</v>
@@ -2236,50 +2232,36 @@
     </row>
     <row r="18" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="2:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>12</v>
-      </c>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -2422,19 +2404,9 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I10" r:id="rId1" display="Evidence: " xr:uid="{37B378A6-28BF-456A-B609-75C3F0AFBA61}"/>
+    <hyperlink ref="I9" r:id="rId1" display="Evidence: " xr:uid="{37B378A6-28BF-456A-B609-75C3F0AFBA61}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documentation/Testing/Testing.xlsx
+++ b/Documentation/Testing/Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diarmuid\Desktop\SETU_Code_Lab\Documentation\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B56E450-C87C-421F-A90B-0C3B31AF4EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D135F784-AC90-42F2-968A-864F6D94592F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{AEF770C7-57FF-4E6E-9271-55DC3BE5003D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="194">
   <si>
     <t>TEST ID</t>
   </si>
@@ -534,9 +534,6 @@
     <t>Full flow completed in ≤ 5 minutes (300 seconds)</t>
   </si>
   <si>
-    <t xml:space="preserve">Full flow completed in </t>
-  </si>
-  <si>
     <t>Reliability</t>
   </si>
   <si>
@@ -740,6 +737,9 @@
   </si>
   <si>
     <t>Uptime is 99.69%</t>
+  </si>
+  <si>
+    <t>Full flow completed in roughly 2 mins</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="3" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>123</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="4" spans="2:9" ht="120" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>126</v>
@@ -1907,7 +1907,7 @@
         <v>129</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>12</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="5" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>126</v>
@@ -1931,29 +1931,31 @@
         <v>132</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>12</v>
@@ -1962,22 +1964,22 @@
     </row>
     <row r="7" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>12</v>
@@ -1986,22 +1988,22 @@
     </row>
     <row r="8" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>12</v>
@@ -2010,48 +2012,48 @@
     </row>
     <row r="9" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="135" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>12</v>
@@ -2060,22 +2062,22 @@
     </row>
     <row r="11" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>12</v>
@@ -2084,22 +2086,22 @@
     </row>
     <row r="12" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>12</v>
@@ -2108,22 +2110,22 @@
     </row>
     <row r="13" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>12</v>
@@ -2132,74 +2134,74 @@
     </row>
     <row r="14" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="150" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>12</v>
@@ -2208,22 +2210,22 @@
     </row>
     <row r="17" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>12</v>
@@ -2232,22 +2234,22 @@
     </row>
     <row r="18" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>12</v>
